--- a/examples/01-basic-data.xlsx
+++ b/examples/01-basic-data.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sales'!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +19,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₴&quot;"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="hh:mm"/>
+    <numFmt numFmtId="172" formatCode="[hh]:mm:ss"/>
+    <numFmt numFmtId="173" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,13 +69,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +465,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,11 +500,21 @@
           <t>In stock</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>Widget 01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -495,13 +532,18 @@
         <v>46027</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gadget</t>
+          <t>Gadget 02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -510,22 +552,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>24.5</v>
+        <v>24.99</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46034</v>
+        <v>46037</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>00037</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gizmo</t>
+          <t>Gizmo 03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,22 +586,32 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14.25</v>
+        <v>14.82</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46056</v>
+        <v>46062</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>00074</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Support plan</t>
+          <t>Support plan 04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -558,22 +620,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>199</v>
+        <v>210.94</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46073</v>
+        <v>46082</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>00111</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Training 05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -582,22 +649,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46090</v>
+        <v>46102</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>00148</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Консультація</t>
+          <t>Консультація 06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -606,20 +683,1490 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>00185</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Widget 07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>840</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>00222</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gadget 08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>00259</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gizmo 09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>160</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>00296</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Support plan 10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>234.82</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>00333</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Training 11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46120</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>00370</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Консультація 12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>00407</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Widget 13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>720</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>00444</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gadget 14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>315</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46073</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>00481</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gizmo 15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>00518</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Support plan 16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>00555</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Training 17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>00592</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Консультація 18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1608</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>00629</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" outlineLevel="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Widget 19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>600</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>00666</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gadget 20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>270</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>00703</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gizmo 21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>560</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46116</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>00740</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Support plan 22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>282.58</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>00777</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Training 23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>00814</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" hidden="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Консультація 24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1752</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46180</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>00851</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Widget 25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>480</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>00888</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gadget 26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>225</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46109</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>00925</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gizmo 27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>480</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46134</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Support plan 28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>84</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>306.46</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>00999</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Training 29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>00036</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Консультація 30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1896</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>00073</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Widget 31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>360</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46117</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>00110</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gadget 32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>180</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>00147</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gizmo 33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>400</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>00184</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>North region</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Support plan 34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>72</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46172</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>00221</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Training 35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>00258</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Консультація 36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Послуги</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46111</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
+      <c r="D37" s="2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>00295</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>West region</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Widget 37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>240</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>00332</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gadget 38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>135</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>00369</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>South region</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gizmo 39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>320</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>00406</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>East region</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Support plan 40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>60</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>00443</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:H41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>-1234567</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>#,##0;[Red]-#,##0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>123456789012345</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1.234e-06</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.00E+00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fraction</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t># ?/?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>1999.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>#,##0.00 "₴"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>-45.1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>_-* #,##0.00_-;-* #,##0.00_-;_-* "-"??_-;_-@_-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>46081</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dd.mm.yyyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Date and time</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>46082.60434027778</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yyyy-mm-dd hh:mm:ss</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hh:mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>1.086805555555556</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[h]:mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="B16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Text as number</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>00123</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Multi-line</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>First line
+Second line</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Українська</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Привіт, світе</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>こんにちは</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Emoji</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ready ✅ 🚀</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Long text</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, Lorem ipsum dolor sit amet, </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/01-basic-data.xlsx
+++ b/examples/01-basic-data.xlsx
@@ -95,6 +95,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -467,6 +476,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col hidden="1" width="8" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col hidden="1" min="9" max="9" width="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,7 +681,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>Консультація 06</t>
@@ -865,7 +875,7 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1">
+    <row r="13" hidden="1" outlineLevel="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>Консультація 12</t>
@@ -1059,7 +1069,7 @@
         </is>
       </c>
     </row>
-    <row r="19" outlineLevel="1">
+    <row r="19" hidden="1" outlineLevel="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>Консультація 18</t>
@@ -1447,7 +1457,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>Консультація 30</t>
@@ -1641,7 +1651,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>Консультація 36</t>
@@ -1802,7 +1812,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H41"/>
+  <autoFilter ref="A1:H41">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Hardware"/>
+        <filter val="Services"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6" hiddenButton="0" showButton="1">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState ref="A2:H41">
+      <sortCondition descending="1" ref="D2:D41"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
